--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jupyter\tunnel-monitoring-platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4208488D-0305-4D6B-9F08-B8BD82C32B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA63766-4DC3-4389-A988-92F72EEEE81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="实时变形量类数据" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="11">
   <si>
     <t>时间</t>
   </si>
@@ -917,11 +917,8 @@
       <c r="I16">
         <v>0.62239999999999995</v>
       </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>46128.625</v>
       </c>
@@ -949,11 +946,8 @@
       <c r="I17">
         <v>0.26250000000000001</v>
       </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46128.666666666701</v>
       </c>
@@ -981,11 +975,8 @@
       <c r="I18">
         <v>0.64729999999999999</v>
       </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>46128.708333333299</v>
       </c>
@@ -1013,11 +1004,8 @@
       <c r="I19">
         <v>0.2339</v>
       </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>46128.75</v>
       </c>
@@ -1045,11 +1033,8 @@
       <c r="I20">
         <v>0.30640000000000001</v>
       </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46128.791666666701</v>
       </c>
@@ -1077,11 +1062,8 @@
       <c r="I21">
         <v>0.74319999999999997</v>
       </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46128.833333333299</v>
       </c>
@@ -1109,11 +1091,8 @@
       <c r="I22">
         <v>0.63229999999999997</v>
       </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>46128.875</v>
       </c>
@@ -1132,11 +1111,8 @@
       <c r="I23">
         <v>-1.4177999999999999</v>
       </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>46128.916666666701</v>
       </c>
@@ -1164,11 +1140,8 @@
       <c r="I24">
         <v>0.88090000000000002</v>
       </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>46128.958333333299</v>
       </c>
@@ -1191,7 +1164,7 @@
         <v>3.1199999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>46129</v>
       </c>
@@ -1219,11 +1192,8 @@
       <c r="I26">
         <v>0.80269999999999997</v>
       </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>46129.041666666701</v>
       </c>
@@ -1246,7 +1216,7 @@
         <v>2.8899999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>46129.083333333299</v>
       </c>
@@ -1269,7 +1239,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>46129.125</v>
       </c>
@@ -1289,7 +1259,7 @@
         <v>0.1431</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>46129.166666666701</v>
       </c>
@@ -1312,7 +1282,7 @@
         <v>-0.12620000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>46129.208333333299</v>
       </c>
@@ -1340,11 +1310,8 @@
       <c r="I31">
         <v>0.91090000000000004</v>
       </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>46129.25</v>
       </c>
@@ -1371,9 +1338,6 @@
       </c>
       <c r="I32">
         <v>0.91159999999999997</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1404,9 +1368,6 @@
       <c r="I33">
         <v>0.90700000000000003</v>
       </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -1436,9 +1397,6 @@
       <c r="I34">
         <v>0.84430000000000005</v>
       </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -1462,12 +1420,6 @@
       <c r="G35">
         <v>-1.2500000000000001E-2</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
@@ -1537,12 +1489,6 @@
       <c r="G38">
         <v>4.3700000000000003E-2</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
@@ -1632,9 +1578,6 @@
       <c r="I42">
         <v>0.95669999999999999</v>
       </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
@@ -1661,9 +1604,6 @@
       <c r="I43">
         <v>0.8075</v>
       </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
@@ -1690,9 +1630,6 @@
       <c r="I44">
         <v>1.1397999999999999</v>
       </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
@@ -1719,9 +1656,6 @@
       <c r="I45">
         <v>1.1391</v>
       </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
@@ -1784,7 +1718,7 @@
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>46129.916666666701</v>
       </c>
@@ -1812,11 +1746,8 @@
       <c r="I49">
         <v>-0.96889999999999998</v>
       </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>46129.958333333299</v>
       </c>
@@ -1844,11 +1775,8 @@
       <c r="I50">
         <v>-0.82989999999999997</v>
       </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>46130</v>
       </c>
@@ -1876,11 +1804,8 @@
       <c r="I51">
         <v>-0.82609999999999995</v>
       </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>46130.041666666701</v>
       </c>
@@ -1908,11 +1833,8 @@
       <c r="I52">
         <v>-0.83689999999999998</v>
       </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>46130.083333333299</v>
       </c>
@@ -1940,11 +1862,8 @@
       <c r="I53">
         <v>-0.72619999999999996</v>
       </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>46130.125</v>
       </c>
@@ -1972,11 +1891,8 @@
       <c r="I54">
         <v>-0.86280000000000001</v>
       </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>46130.166666666701</v>
       </c>
@@ -2004,11 +1920,8 @@
       <c r="I55">
         <v>-0.75670000000000004</v>
       </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>46130.208333333299</v>
       </c>
@@ -2036,11 +1949,8 @@
       <c r="I56">
         <v>-0.74339999999999995</v>
       </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>46130.25</v>
       </c>
@@ -2062,14 +1972,8 @@
       <c r="G57">
         <v>0.33579999999999999</v>
       </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>46130.291666666701</v>
       </c>
@@ -2091,14 +1995,8 @@
       <c r="G58">
         <v>0.1648</v>
       </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>46130.333333333299</v>
       </c>
@@ -2114,14 +2012,8 @@
       <c r="F59">
         <v>0.19259999999999999</v>
       </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>46130.375</v>
       </c>
@@ -2149,11 +2041,8 @@
       <c r="I60" t="s">
         <v>1</v>
       </c>
-      <c r="J60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>46130.416666666701</v>
       </c>
@@ -2181,11 +2070,8 @@
       <c r="I61">
         <v>-1.0900000000000001</v>
       </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>46130.458333333299</v>
       </c>
@@ -2210,11 +2096,8 @@
       <c r="I62" t="s">
         <v>1</v>
       </c>
-      <c r="J62" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>46130.5</v>
       </c>
@@ -2239,11 +2122,8 @@
       <c r="I63">
         <v>-0.90629999999999999</v>
       </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>46130.541666666701</v>
       </c>
@@ -2267,9 +2147,6 @@
       </c>
       <c r="I64">
         <v>-1.1157999999999999</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -2297,9 +2174,6 @@
       <c r="I65">
         <v>2.1499999999999998E-2</v>
       </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
@@ -2326,9 +2200,6 @@
       <c r="I66">
         <v>2.0750000000000002</v>
       </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
@@ -2355,9 +2226,6 @@
       <c r="I67">
         <v>1.9176</v>
       </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
@@ -2555,9 +2423,6 @@
       <c r="I74">
         <v>1.9603999999999999</v>
       </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
@@ -2581,9 +2446,6 @@
       <c r="I75" t="s">
         <v>1</v>
       </c>
-      <c r="J75" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
@@ -2607,9 +2469,6 @@
       <c r="I76">
         <v>2.1694</v>
       </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
@@ -2633,9 +2492,6 @@
       <c r="I77" t="s">
         <v>1</v>
       </c>
-      <c r="J77" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
@@ -2659,9 +2515,6 @@
       <c r="I78">
         <v>1.7628999999999999</v>
       </c>
-      <c r="J78">
-        <v>0</v>
-      </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
@@ -2685,9 +2538,6 @@
       <c r="I79">
         <v>1.8692</v>
       </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
@@ -2714,9 +2564,6 @@
       <c r="I80">
         <v>2.08</v>
       </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
@@ -2743,9 +2590,6 @@
       <c r="I81">
         <v>2.1543000000000001</v>
       </c>
-      <c r="J81">
-        <v>0</v>
-      </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
@@ -2769,9 +2613,6 @@
       <c r="I82">
         <v>1.9957</v>
       </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
@@ -2798,9 +2639,6 @@
       <c r="I83" t="s">
         <v>1</v>
       </c>
-      <c r="J83" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
@@ -2821,12 +2659,6 @@
       <c r="F84">
         <v>-2.7894000000000001</v>
       </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
-      <c r="J84">
-        <v>0</v>
-      </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
@@ -2850,12 +2682,6 @@
       <c r="H85">
         <v>-1.8250999999999999</v>
       </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
@@ -2879,12 +2705,6 @@
       <c r="H86">
         <v>-1.0711999999999999</v>
       </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="J86">
-        <v>0</v>
-      </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
@@ -2908,12 +2728,6 @@
       <c r="H87" t="s">
         <v>1</v>
       </c>
-      <c r="I87" t="s">
-        <v>1</v>
-      </c>
-      <c r="J87" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
@@ -2937,12 +2751,6 @@
       <c r="H88">
         <v>-2.6751</v>
       </c>
-      <c r="I88">
-        <v>0</v>
-      </c>
-      <c r="J88">
-        <v>0</v>
-      </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
@@ -2966,12 +2774,6 @@
       <c r="H89">
         <v>-4.3400000000000001E-2</v>
       </c>
-      <c r="I89">
-        <v>0</v>
-      </c>
-      <c r="J89">
-        <v>0</v>
-      </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
@@ -2995,12 +2797,6 @@
       <c r="H90">
         <v>-1.3228</v>
       </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
@@ -3520,12 +3316,6 @@
       <c r="F111">
         <v>-2.8519000000000001</v>
       </c>
-      <c r="I111">
-        <v>0</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
@@ -3543,12 +3333,6 @@
       <c r="F112">
         <v>-2.9085000000000001</v>
       </c>
-      <c r="I112">
-        <v>0</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
@@ -3569,12 +3353,6 @@
       <c r="F113">
         <v>-3.0487000000000002</v>
       </c>
-      <c r="I113" t="s">
-        <v>1</v>
-      </c>
-      <c r="J113" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
@@ -3592,12 +3370,6 @@
       <c r="F114">
         <v>-3.0447000000000002</v>
       </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
-      </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
@@ -3612,12 +3384,6 @@
       <c r="F115">
         <v>-3.0129999999999999</v>
       </c>
-      <c r="I115" t="s">
-        <v>1</v>
-      </c>
-      <c r="J115" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
@@ -3631,12 +3397,6 @@
       </c>
       <c r="F116">
         <v>-3.2692999999999999</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20338"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jupyter\tunnel-monitoring-platform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA63766-4DC3-4389-A988-92F72EEEE81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2071C8D-BA4A-4836-A22E-434C1E39011B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="实时变形量类数据" sheetId="1" r:id="rId1"/>
     <sheet name="每天变形速率数据" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="179021"/>
 </workbook>
 </file>
 
@@ -461,12 +450,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J123"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.453125" customWidth="1"/>
-    <col min="2" max="7" width="29.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.44140625" customWidth="1"/>
+    <col min="2" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1558,7 +1547,7 @@
         <v>46129.666666666701</v>
       </c>
       <c r="B42">
-        <v>0.87970000000000004</v>
+        <v>-1.8796999999999999</v>
       </c>
       <c r="C42">
         <v>-0.2288</v>
@@ -1584,7 +1573,7 @@
         <v>46129.708333333299</v>
       </c>
       <c r="B43">
-        <v>0.90429999999999999</v>
+        <v>-1.9043000000000001</v>
       </c>
       <c r="C43">
         <v>-0.2306</v>
@@ -1610,7 +1599,7 @@
         <v>46129.75</v>
       </c>
       <c r="B44">
-        <v>0.19320000000000001</v>
+        <v>-1.1932</v>
       </c>
       <c r="C44">
         <v>0.32379999999999998</v>
@@ -1636,7 +1625,7 @@
         <v>46129.791666666701</v>
       </c>
       <c r="B45">
-        <v>0.1774</v>
+        <v>-1.1774</v>
       </c>
       <c r="C45">
         <v>-0.10349999999999999</v>
@@ -1662,7 +1651,7 @@
         <v>46129.833333333299</v>
       </c>
       <c r="B46">
-        <v>0.1613</v>
+        <v>-1.1613</v>
       </c>
       <c r="C46">
         <v>-0.10879999999999999</v>
@@ -1691,7 +1680,7 @@
         <v>46129.875</v>
       </c>
       <c r="B47">
-        <v>-0.42870000000000003</v>
+        <v>-1.4287000000000001</v>
       </c>
       <c r="C47">
         <v>7.1300000000000002E-2</v>
@@ -1723,7 +1712,7 @@
         <v>46129.916666666701</v>
       </c>
       <c r="B49">
-        <v>-0.77839999999999998</v>
+        <v>-1.7784</v>
       </c>
       <c r="C49">
         <v>4.3200000000000002E-2</v>
@@ -1752,7 +1741,7 @@
         <v>46129.958333333299</v>
       </c>
       <c r="B50">
-        <v>-0.91449999999999998</v>
+        <v>-1.9145000000000001</v>
       </c>
       <c r="C50">
         <v>-7.0199999999999999E-2</v>
@@ -3158,7 +3147,7 @@
         <v>46132.25</v>
       </c>
       <c r="B105">
-        <v>-1.8585</v>
+        <v>-2.8584999999999998</v>
       </c>
       <c r="C105">
         <v>-2.3140000000000001</v>
@@ -3181,7 +3170,7 @@
         <v>46132.291666666701</v>
       </c>
       <c r="B106">
-        <v>-1.7315</v>
+        <v>-2.7315</v>
       </c>
       <c r="C106">
         <v>-2.2991999999999999</v>
@@ -3204,7 +3193,7 @@
         <v>46132.333333333299</v>
       </c>
       <c r="B107">
-        <v>-1.5706</v>
+        <v>-2.5706000000000002</v>
       </c>
       <c r="C107">
         <v>-2.2801999999999998</v>
@@ -3259,7 +3248,7 @@
         <v>46132.416666666701</v>
       </c>
       <c r="B109">
-        <v>-1.6305000000000001</v>
+        <v>-2.6305000000000001</v>
       </c>
       <c r="C109">
         <v>-2.2963</v>
@@ -3282,7 +3271,7 @@
         <v>46132.458333333299</v>
       </c>
       <c r="B110">
-        <v>-1.5750999999999999</v>
+        <v>-2.5750999999999999</v>
       </c>
       <c r="C110">
         <v>-2.2408000000000001</v>
@@ -3305,7 +3294,7 @@
         <v>46132.5</v>
       </c>
       <c r="B111">
-        <v>-1.0859000000000001</v>
+        <v>-2.0859000000000001</v>
       </c>
       <c r="C111">
         <v>-2.2776999999999998</v>
@@ -3322,7 +3311,7 @@
         <v>46132.541666666701</v>
       </c>
       <c r="B112">
-        <v>-1.5907</v>
+        <v>-2.5907</v>
       </c>
       <c r="C112">
         <v>-2.3748</v>
@@ -3345,7 +3334,7 @@
         <v>-2.4331</v>
       </c>
       <c r="D113">
-        <v>-0.55059999999999998</v>
+        <v>-1.5506</v>
       </c>
       <c r="E113">
         <v>-2.3127</v>
@@ -3536,7 +3525,7 @@
         <v>46133.416666666701</v>
       </c>
       <c r="B123">
-        <v>-1.2017</v>
+        <v>-2.2017000000000002</v>
       </c>
       <c r="C123">
         <v>-2.4386999999999999</v>
@@ -3554,18 +3543,19 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5D85E8-5610-4917-8D0A-C168237EFB9B}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.453125" customWidth="1"/>
-    <col min="2" max="7" width="29.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.44140625" customWidth="1"/>
+    <col min="2" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20338"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jupyter\tunnel-monitoring-platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2071C8D-BA4A-4836-A22E-434C1E39011B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114716EB-AEC1-444C-9CA2-1571259A5D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="实时变形量类数据" sheetId="1" r:id="rId1"/>
@@ -450,12 +450,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J123"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.44140625" customWidth="1"/>
-    <col min="2" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.453125" customWidth="1"/>
+    <col min="2" max="7" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="29.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -507,7 +507,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="I2">
-        <v>0.2084</v>
+        <v>-0.2084</v>
       </c>
       <c r="J2">
         <v>0.81940000000000002</v>
@@ -530,7 +530,7 @@
         <v>-4.7100000000000003E-2</v>
       </c>
       <c r="I3">
-        <v>0.106</v>
+        <v>-0.106</v>
       </c>
       <c r="J3">
         <v>0.57850000000000001</v>
@@ -553,7 +553,7 @@
         <v>9.7000000000000003E-3</v>
       </c>
       <c r="I4">
-        <v>0.1074</v>
+        <v>-0.1074</v>
       </c>
       <c r="J4">
         <v>0.39250000000000002</v>
@@ -576,7 +576,7 @@
         <v>3.0800000000000001E-2</v>
       </c>
       <c r="I5">
-        <v>0.1512</v>
+        <v>-0.1512</v>
       </c>
       <c r="J5">
         <v>0.37230000000000002</v>
@@ -599,7 +599,7 @@
         <v>-3.0200000000000001E-2</v>
       </c>
       <c r="I6">
-        <v>0.16470000000000001</v>
+        <v>-0.16470000000000001</v>
       </c>
       <c r="J6">
         <v>0.3367</v>
@@ -631,7 +631,7 @@
         <v>-0.41710000000000003</v>
       </c>
       <c r="I7">
-        <v>0.18490000000000001</v>
+        <v>-0.18490000000000001</v>
       </c>
       <c r="J7">
         <v>0.41439999999999999</v>
@@ -663,7 +663,7 @@
         <v>-0.36530000000000001</v>
       </c>
       <c r="I8">
-        <v>0.21190000000000001</v>
+        <v>-0.21190000000000001</v>
       </c>
       <c r="J8">
         <v>0.44009999999999999</v>
@@ -695,7 +695,7 @@
         <v>-4.19E-2</v>
       </c>
       <c r="I9">
-        <v>0.21970000000000001</v>
+        <v>-0.21970000000000001</v>
       </c>
       <c r="J9">
         <v>0.75729999999999997</v>
@@ -727,7 +727,7 @@
         <v>-0.1585</v>
       </c>
       <c r="I10">
-        <v>0.24260000000000001</v>
+        <v>-0.24260000000000001</v>
       </c>
       <c r="J10">
         <v>0.56459999999999999</v>
@@ -759,7 +759,7 @@
         <v>-0.44800000000000001</v>
       </c>
       <c r="I11">
-        <v>0.21479999999999999</v>
+        <v>-0.21479999999999999</v>
       </c>
       <c r="J11">
         <v>0.52869999999999995</v>
@@ -791,7 +791,7 @@
         <v>-0.47849999999999998</v>
       </c>
       <c r="I12">
-        <v>0.2102</v>
+        <v>-0.2102</v>
       </c>
       <c r="J12">
         <v>0.61150000000000004</v>
@@ -823,7 +823,7 @@
         <v>-0.27900000000000003</v>
       </c>
       <c r="I13">
-        <v>0.20230000000000001</v>
+        <v>-0.20230000000000001</v>
       </c>
       <c r="J13">
         <v>0.55759999999999998</v>
@@ -855,7 +855,7 @@
         <v>-0.4748</v>
       </c>
       <c r="I14">
-        <v>0.21679999999999999</v>
+        <v>-0.21679999999999999</v>
       </c>
       <c r="J14">
         <v>0.4506</v>
@@ -904,7 +904,7 @@
         <v>-0.2833</v>
       </c>
       <c r="I16">
-        <v>0.62239999999999995</v>
+        <v>-0.62239999999999995</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="I17">
-        <v>0.26250000000000001</v>
+        <v>-0.26250000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -962,7 +962,7 @@
         <v>-2.8500000000000001E-2</v>
       </c>
       <c r="I18">
-        <v>0.64729999999999999</v>
+        <v>-0.64729999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -991,7 +991,7 @@
         <v>-0.35780000000000001</v>
       </c>
       <c r="I19">
-        <v>0.2339</v>
+        <v>-0.2339</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1020,7 +1020,7 @@
         <v>-3.0999999999999999E-3</v>
       </c>
       <c r="I20">
-        <v>0.30640000000000001</v>
+        <v>-0.30640000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1049,7 +1049,7 @@
         <v>-0.19950000000000001</v>
       </c>
       <c r="I21">
-        <v>0.74319999999999997</v>
+        <v>-0.74319999999999997</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1078,7 +1078,7 @@
         <v>-0.4365</v>
       </c>
       <c r="I22">
-        <v>0.63229999999999997</v>
+        <v>-0.63229999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1127,7 +1127,7 @@
         <v>-0.49220000000000003</v>
       </c>
       <c r="I24">
-        <v>0.88090000000000002</v>
+        <v>-0.88090000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1179,7 +1179,7 @@
         <v>-0.15629999999999999</v>
       </c>
       <c r="I26">
-        <v>0.80269999999999997</v>
+        <v>-0.80269999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1297,7 +1297,7 @@
         <v>-0.42280000000000001</v>
       </c>
       <c r="I31">
-        <v>0.91090000000000004</v>
+        <v>-0.91090000000000004</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1326,7 +1326,7 @@
         <v>-0.37930000000000003</v>
       </c>
       <c r="I32">
-        <v>0.91159999999999997</v>
+        <v>-0.91159999999999997</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1355,7 +1355,7 @@
         <v>-0.65949999999999998</v>
       </c>
       <c r="I33">
-        <v>0.90700000000000003</v>
+        <v>-0.90700000000000003</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1384,7 +1384,7 @@
         <v>-0.5917</v>
       </c>
       <c r="I34">
-        <v>0.84430000000000005</v>
+        <v>-0.84430000000000005</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1565,7 +1565,7 @@
         <v>-0.1479</v>
       </c>
       <c r="I42">
-        <v>0.95669999999999999</v>
+        <v>-0.95669999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -1591,7 +1591,7 @@
         <v>-0.2087</v>
       </c>
       <c r="I43">
-        <v>0.8075</v>
+        <v>-0.8075</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -1617,7 +1617,7 @@
         <v>-0.41210000000000002</v>
       </c>
       <c r="I44">
-        <v>1.1397999999999999</v>
+        <v>-1.1397999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -1643,7 +1643,7 @@
         <v>-0.30430000000000001</v>
       </c>
       <c r="I45">
-        <v>1.1391</v>
+        <v>-1.1391</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -1669,7 +1669,7 @@
         <v>-0.2707</v>
       </c>
       <c r="I46">
-        <v>1.1060000000000001</v>
+        <v>-1.1060000000000001</v>
       </c>
       <c r="J46">
         <v>8.3999999999999995E-3</v>
@@ -1698,7 +1698,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="I47">
-        <v>0.90700000000000003</v>
+        <v>-0.90700000000000003</v>
       </c>
       <c r="J47">
         <v>5.2200000000000003E-2</v>
@@ -2161,7 +2161,7 @@
         <v>-0.73640000000000005</v>
       </c>
       <c r="I65">
-        <v>2.1499999999999998E-2</v>
+        <v>-2.1499999999999998E-2</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -2187,7 +2187,7 @@
         <v>-1.6903999999999999</v>
       </c>
       <c r="I66">
-        <v>2.0750000000000002</v>
+        <v>-2.0750000000000002</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -2213,7 +2213,7 @@
         <v>-1.7676000000000001</v>
       </c>
       <c r="I67">
-        <v>1.9176</v>
+        <v>-1.9176</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -2410,7 +2410,7 @@
         <v>-2.6977000000000002</v>
       </c>
       <c r="I74">
-        <v>1.9603999999999999</v>
+        <v>-1.9603999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -2456,7 +2456,7 @@
         <v>-2.7755000000000001</v>
       </c>
       <c r="I76">
-        <v>2.1694</v>
+        <v>-2.1694</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -2502,7 +2502,7 @@
         <v>-2.6636000000000002</v>
       </c>
       <c r="I78">
-        <v>1.7628999999999999</v>
+        <v>-1.7628999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -2525,7 +2525,7 @@
         <v>-2.6920999999999999</v>
       </c>
       <c r="I79">
-        <v>1.8692</v>
+        <v>-1.8692</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -2551,7 +2551,7 @@
         <v>-1.5674999999999999</v>
       </c>
       <c r="I80">
-        <v>2.08</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -2577,7 +2577,7 @@
         <v>-1.7155</v>
       </c>
       <c r="I81">
-        <v>2.1543000000000001</v>
+        <v>-2.1543000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -2600,7 +2600,7 @@
         <v>-2.7181000000000002</v>
       </c>
       <c r="I82">
-        <v>1.9957</v>
+        <v>-1.9957</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -3550,12 +3550,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5D85E8-5610-4917-8D0A-C168237EFB9B}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.44140625" customWidth="1"/>
-    <col min="2" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.453125" customWidth="1"/>
+    <col min="2" max="7" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="29.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
